--- a/VerveStacks_NGA/SysSettings.xlsx
+++ b/VerveStacks_NGA/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7014C7-CBE3-4A25-9613-7753A227A794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DBE9D8-6BB6-4B92-9211-67BD0B07BE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="368">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -677,6 +677,24 @@
   </si>
   <si>
     <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>~tfm_comgrp</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
   </si>
   <si>
     <t>NGA</t>
@@ -3514,7 +3532,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3597,7 +3615,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3629,10 +3647,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="O5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3641,7 +3659,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3658,10 +3676,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3670,7 +3688,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3687,10 +3705,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3699,7 +3717,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3716,10 +3734,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="O8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3728,7 +3746,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -3745,10 +3763,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3757,7 +3775,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -3774,10 +3792,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="O10" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -3786,7 +3804,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -3803,10 +3821,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O11" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -3815,7 +3833,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -3832,10 +3850,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -3844,7 +3862,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -3861,10 +3879,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O13" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -3873,7 +3891,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -3893,10 +3911,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O14" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -3905,7 +3923,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -3925,10 +3943,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -3937,7 +3955,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -3966,10 +3984,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -3978,7 +3996,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -3998,10 +4016,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="O17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -4010,7 +4028,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -4030,10 +4048,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="O18" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -4042,7 +4060,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -4062,10 +4080,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O19" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -4074,7 +4092,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -4094,10 +4112,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="O20" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -4106,7 +4124,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -4132,10 +4150,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O21" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -4144,7 +4162,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -4164,10 +4182,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -4176,7 +4194,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -4193,10 +4211,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -4205,7 +4223,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -4222,10 +4240,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -4234,7 +4252,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -4242,10 +4260,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -4254,7 +4272,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -4262,10 +4280,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -4274,7 +4292,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -4282,10 +4300,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="O27" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -4294,18 +4312,23 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="17.649999999999999" thickBot="1">
+      <c r="B28" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="M28" t="s">
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="O28" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -4314,18 +4337,27 @@
         <v>35</v>
       </c>
       <c r="R28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="M29" t="s">
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -4334,18 +4366,27 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="30" spans="2:18">
+      <c r="D30" t="s">
+        <v>216</v>
+      </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -4354,7 +4395,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -4362,10 +4403,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="O31" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -4374,7 +4415,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -4382,10 +4423,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -4394,7 +4435,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -4402,10 +4443,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -4414,7 +4455,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -4422,10 +4463,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -4434,7 +4475,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -4442,10 +4483,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O35" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -4454,7 +4495,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -4462,10 +4503,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="O36" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -4474,7 +4515,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -4482,10 +4523,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -4494,7 +4535,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -4502,10 +4543,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="O38" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -4514,7 +4555,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -4522,10 +4563,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -4534,7 +4575,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -4542,10 +4583,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="O40" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -4554,7 +4595,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -4562,10 +4603,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="O41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -4574,7 +4615,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -4582,10 +4623,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O42" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -4594,7 +4635,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -4602,10 +4643,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="O43" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -4614,7 +4655,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -4622,10 +4663,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O44" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -4634,7 +4675,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -4642,10 +4683,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O45" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -4654,7 +4695,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -4662,10 +4703,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="O46" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -4674,7 +4715,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -4682,10 +4723,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="O47" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -4694,7 +4735,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -4702,10 +4743,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="O48" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -4714,7 +4755,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -4722,10 +4763,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="O49" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -4734,7 +4775,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -4742,10 +4783,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O50" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -4754,7 +4795,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -4762,10 +4803,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -4774,7 +4815,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -4782,10 +4823,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="O52" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -4794,7 +4835,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -4802,10 +4843,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="O53" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -4814,7 +4855,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -4822,10 +4863,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -4834,7 +4875,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -4842,10 +4883,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O55" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -4854,7 +4895,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -4862,10 +4903,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O56" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -4874,7 +4915,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -4882,10 +4923,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="O57" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -4894,7 +4935,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -4902,10 +4943,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="O58" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -4914,7 +4955,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -4922,10 +4963,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O59" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -4934,7 +4975,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -4942,10 +4983,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="O60" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -4954,7 +4995,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -4962,10 +5003,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="O61" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -4974,7 +5015,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -4982,10 +5023,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="O62" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -4994,7 +5035,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -5002,10 +5043,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="O63" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -5014,7 +5055,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -5022,10 +5063,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="O64" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -5034,7 +5075,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -5042,10 +5083,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="O65" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -5054,7 +5095,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -5062,10 +5103,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="O66" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -5074,7 +5115,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -5082,10 +5123,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="O67" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -5094,7 +5135,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -5102,10 +5143,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="O68" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -5114,7 +5155,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="13:18">
@@ -5122,10 +5163,10 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="O69" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
@@ -5134,7 +5175,7 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="13:18">
@@ -5142,10 +5183,10 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="O70" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
@@ -5154,7 +5195,7 @@
         <v>35</v>
       </c>
       <c r="R70" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="13:18">
@@ -5162,10 +5203,10 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O71" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
@@ -5174,7 +5215,7 @@
         <v>35</v>
       </c>
       <c r="R71" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="13:18">
@@ -5182,10 +5223,10 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="O72" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
@@ -5194,7 +5235,7 @@
         <v>35</v>
       </c>
       <c r="R72" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="13:18">
@@ -5202,10 +5243,10 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="O73" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
@@ -5214,7 +5255,7 @@
         <v>35</v>
       </c>
       <c r="R73" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="13:18">
@@ -5222,10 +5263,10 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="O74" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
@@ -5234,7 +5275,7 @@
         <v>35</v>
       </c>
       <c r="R74" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="13:18">
@@ -5242,10 +5283,10 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="O75" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
@@ -5254,7 +5295,7 @@
         <v>35</v>
       </c>
       <c r="R75" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="13:18">
@@ -5262,10 +5303,10 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="O76" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
@@ -5274,7 +5315,7 @@
         <v>35</v>
       </c>
       <c r="R76" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="13:18">
@@ -5282,10 +5323,10 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="O77" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
@@ -5294,7 +5335,7 @@
         <v>35</v>
       </c>
       <c r="R77" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
